--- a/InputExample.xlsx
+++ b/InputExample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janburianek/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janburianek/Projects/CashFlowViz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BFEE2E3-811A-C844-8737-BAD292083B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A17C4E2-DFA8-3A48-9E09-FEBFA172D3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20280" yWindow="5460" windowWidth="28240" windowHeight="17240" xr2:uid="{D6FAB51D-F143-6D4A-8384-8535D8013602}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Proj 1</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>STATUS</t>
+  </si>
+  <si>
+    <t>Hala nájem</t>
   </si>
 </sst>
 </file>
@@ -68,7 +71,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;Kč&quot;_-;\-* #,##0.00\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0\ &quot;Kč&quot;_-;\-* #,##0\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;Kč&quot;_-;\-* #,##0\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -119,7 +122,7 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -457,11 +460,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4904BBF0-813C-5A48-ABFD-FDD141CD3DAA}">
-  <dimension ref="B2:D6"/>
+  <dimension ref="B2:D7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.2">
@@ -519,6 +522,17 @@
         <v>-140000</v>
       </c>
     </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D7" s="2">
+        <v>-500000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/InputExample.xlsx
+++ b/InputExample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janburianek/Projects/CashFlowViz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A17C4E2-DFA8-3A48-9E09-FEBFA172D3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528DD99A-9116-3646-A1E3-2ED064F06737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20280" yWindow="5460" windowWidth="28240" windowHeight="17240" xr2:uid="{D6FAB51D-F143-6D4A-8384-8535D8013602}"/>
+    <workbookView xWindow="22020" yWindow="7680" windowWidth="28240" windowHeight="17240" xr2:uid="{D6FAB51D-F143-6D4A-8384-8535D8013602}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>Proj 1</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Hala nájem</t>
+  </si>
+  <si>
+    <t>Neflix FR</t>
   </si>
 </sst>
 </file>
@@ -460,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4904BBF0-813C-5A48-ABFD-FDD141CD3DAA}">
-  <dimension ref="B2:D7"/>
+  <dimension ref="B2:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
@@ -524,12 +527,67 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46280</v>
+      </c>
+      <c r="D7" s="2">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C8" s="1">
         <v>46266</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D8" s="2">
+        <v>-500000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D9" s="2">
+        <v>-500000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46327</v>
+      </c>
+      <c r="D10" s="2">
+        <v>-500000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46357</v>
+      </c>
+      <c r="D11" s="2">
+        <v>-500000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46388</v>
+      </c>
+      <c r="D12" s="2">
         <v>-500000</v>
       </c>
     </row>

--- a/InputExample.xlsx
+++ b/InputExample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janburianek/Projects/CashFlowViz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528DD99A-9116-3646-A1E3-2ED064F06737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F7EA9D-A4C3-9B4C-B1AF-FC935E17B505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22020" yWindow="7680" windowWidth="28240" windowHeight="17240" xr2:uid="{D6FAB51D-F143-6D4A-8384-8535D8013602}"/>
   </bookViews>
@@ -59,13 +59,13 @@
     <t>Jan B</t>
   </si>
   <si>
-    <t>STATUS</t>
-  </si>
-  <si>
     <t>Hala nájem</t>
   </si>
   <si>
     <t>Neflix FR</t>
+  </si>
+  <si>
+    <t>START</t>
   </si>
 </sst>
 </file>
@@ -483,7 +483,7 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>46251</v>
@@ -527,7 +527,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1">
         <v>46280</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1">
         <v>46266</v>
@@ -549,7 +549,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1">
         <v>46296</v>
@@ -560,7 +560,7 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1">
         <v>46327</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1">
         <v>46357</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1">
         <v>46388</v>

--- a/InputExample.xlsx
+++ b/InputExample.xlsx
@@ -1,109 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janburianek/Projects/CashFlowViz/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F7EA9D-A4C3-9B4C-B1AF-FC935E17B505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="22020" yWindow="7680" windowWidth="28240" windowHeight="17240" xr2:uid="{D6FAB51D-F143-6D4A-8384-8535D8013602}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22020" yWindow="7680" windowWidth="28240" windowHeight="17240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="List1" sheetId="1" r:id="rId1"/>
+    <sheet name="List1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
-  <si>
-    <t>Proj 1</t>
-  </si>
-  <si>
-    <t>Assets</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>IN/OUT</t>
-  </si>
-  <si>
-    <t>Tomáš N</t>
-  </si>
-  <si>
-    <t>Jan B</t>
-  </si>
-  <si>
-    <t>Hala nájem</t>
-  </si>
-  <si>
-    <t>Neflix FR</t>
-  </si>
-  <si>
-    <t>START</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;Kč&quot;_-;\-* #,##0.00\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;Kč&quot;_-;\-* #,##0\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="238"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="238"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -119,30 +61,89 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
     <cellStyle name="Měna" xfId="1" builtinId="4"/>
-    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -462,136 +463,166 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4904BBF0-813C-5A48-ABFD-FDD141CD3DAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col width="6.6640625" customWidth="1" min="1" max="1"/>
+    <col width="13.83203125" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1">
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>FROM</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>AMOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>46251</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="2" t="n">
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1">
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Proj 1</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="2" t="n">
         <v>100000</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tomáš N</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>46260</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="2" t="n">
         <v>-100000</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jan B</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>46273</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="2" t="n">
         <v>-140000</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1">
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Neflix FR</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="2" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1">
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hala nájem</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="2" t="n">
         <v>-500000</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1">
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hala nájem</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>46296</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="2" t="n">
         <v>-500000</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1">
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hala nájem</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>46327</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="2" t="n">
         <v>-500000</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1">
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hala nájem</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>46357</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="2" t="n">
         <v>-500000</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1">
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hala nájem</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
         <v>46388</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="2" t="n">
         <v>-500000</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
 </worksheet>
 </file>